--- a/demo/financials.xlsx
+++ b/demo/financials.xlsx
@@ -10,26 +10,26 @@
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Revenue" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Rate">Inputs!$B$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
   <si>
     <t>Label</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Month</t>
   </si>
   <si>
     <t>Amount</t>
@@ -51,8 +51,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -80,8 +88,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,16 +389,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>0.1</v>
@@ -397,13 +404,16 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>100</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -414,16 +424,16 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -431,7 +441,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>150</v>
@@ -439,7 +449,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <f>B2+B3</f>
@@ -448,7 +458,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <f>B4*Inputs!B2</f>

--- a/demo/financials.xlsx
+++ b/demo/financials.xlsx
@@ -51,6 +51,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0%"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -88,9 +92,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +404,7 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>0.1</v>
       </c>
     </row>
@@ -406,7 +412,7 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>100</v>
       </c>
     </row>
@@ -435,7 +441,7 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>100</v>
       </c>
     </row>
@@ -443,7 +449,7 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>150</v>
       </c>
     </row>
@@ -451,7 +457,7 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <f>B2+B3</f>
         <v>0</v>
       </c>
@@ -460,7 +466,7 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <f>B4*Inputs!B2</f>
         <v>0</v>
       </c>

--- a/demo/financials.xlsx
+++ b/demo/financials.xlsx
@@ -393,8 +393,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="21.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -428,6 +432,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="14.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">

--- a/demo/financials.xlsx
+++ b/demo/financials.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Revenue" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Revenue!$A$1:$B$5</definedName>
     <definedName name="Rate">Inputs!$B$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,6 +480,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/demo/financials.xlsx
+++ b/demo/financials.xlsx
@@ -10,26 +10,27 @@
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
     <sheet name="Revenue" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Revenue!$A$1:$B$5</definedName>
+    <definedName name="Rate">Inputs!$B$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
   <si>
     <t>Label</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Month</t>
   </si>
   <si>
     <t>Amount</t>
@@ -51,8 +52,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0%"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+  </numFmts>
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -80,8 +93,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,32 +394,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" ht="21.75" customHeight="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
         <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
         <v>100</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -412,50 +433,54 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="14.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3">
         <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3">
         <f>B2+B3</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3">
         <f>B4*Inputs!B2</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/demo/financials.xlsx
+++ b/demo/financials.xlsx
@@ -1,87 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" r:id="rId1"/>
-    <sheet name="Revenue" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Headcount" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Revenue!$A$1:$B$5</definedName>
     <definedName name="Rate">Inputs!$B$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inputs'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Revenue'!$A$1:$B$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Revenue'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pipeline'!$A$2:$F$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Pipeline'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Headcount'!$A$2:$F$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Headcount'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Assumptions</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Commission</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="$#,##0"/>
+    <numFmt numFmtId="167" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="11">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri Light"/>
+      <color rgb="001F4E79"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri Light"/>
+      <color rgb="00595959"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
       <sz val="11"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri Light"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -89,22 +124,380 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="001F4E79"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D6DCE4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D6DCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D6DCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D6DCE4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BF8F00"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BF8F00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BF8F00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BF8F00"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D6DCE4"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="001F4E79"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="001F4E79"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="001F4E79"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Billed revenue — trailing six months</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Revenue'!B9</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Revenue'!$A$10:$A$15</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Revenue'!$B$10:$B$15</c:f>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="100"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>USD</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+        </c:title>
+        <c:numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="10"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Priya Shah</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>Board approved the 10% Q3 commission rate on 12 Aug 2026.
+This cell is the named range Rate: Revenue!B5 and the board deck KPI both read it. Change the rate here, never in the deck.
+— Priya Shah, VP Finance</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5940000" cy="2664000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -391,96 +784,1066 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col width="2.5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="2.5" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3">
-        <v>100</v>
+    <row r="2" ht="30" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Northstar Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FY2026 Q3 Board Pack — financial summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Prepared by</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Priya Shah, VP Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>17 August 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Audience</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Board of Directors · Audit &amp; Comp committee</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>CONFIDENTIAL — do not distribute</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Board-approved assumptions; gold cells are editable</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Billed revenue, commission base and trailing billings</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Q4 pipeline by stage with weighted coverage</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Sales ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Headcount</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Q3 plan vs actual by function</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>People ops</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Gold cells are inputs. Everything else is a formula — overwrite an input, not a calculation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="B18:D18"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;9 &amp;K1F4E79Northstar Analytics — FY2026 Q3 Board Pack&amp;R&amp;9 &amp;KC00000CONFIDENTIAL</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K595959Prepared by Priya Shah, VP Finance · 17 August 2026&amp;R&amp;8 &amp;K595959&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="14.7109375" customWidth="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Commission rate — board approved 12 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Unit commission base (per booked seat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Q3 actual, net of hosting + support</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Net revenue retention</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Trailing twelve months, &gt; $25k cohort</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Logo churn (annual)</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>SMB weighted; enterprise 2.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Blended CAC</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>18400</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Sales + marketing / new logos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>CAC payback (months)</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Gross-margin adjusted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Quota per AE</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>780000</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>FY2026 plan, ramped AEs only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>FX (USD/EUR)</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Treasury rate, locked for the quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Gold cells are the only editable inputs on this tab.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;9 &amp;K1F4E79Northstar Analytics — FY2026 Q3 Board Pack&amp;R&amp;9 &amp;KC00000CONFIDENTIAL</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K595959Prepared by Priya Shah, VP Finance · 17 August 2026&amp;R&amp;8 &amp;K595959&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="n">
+        <v>1183400</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="n">
+        <v>1276900</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B4" s="26">
         <f>B2+B3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Commission</t>
+        </is>
+      </c>
+      <c r="B5" s="28">
         <f>B4*Inputs!B2</f>
-        <v>0</v>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Commission = Total billed × Rate (Inputs!B2, named range Rate). Rate is the only cell to touch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Trailing billings — monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Billed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>1312500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>1358900</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>1401200</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>1466800</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n">
+        <v>1524300</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>1583700</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B5"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;9 &amp;K1F4E79Northstar Analytics — FY2026 Q3 Board Pack&amp;R&amp;9 &amp;KC00000CONFIDENTIAL</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K595959Prepared by Priya Shah, VP Finance · 17 August 2026&amp;R&amp;8 &amp;K595959&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D6DCE4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Q4 pipeline by stage — as at 15 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Opps</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>Weighted</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Commentary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>1 — Discovery</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="n">
+        <v>84</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>12640000</v>
+      </c>
+      <c r="D3" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="20">
+        <f>C3*D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>Top of funnel; MQL mix improving</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>2 — Qualified</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="n">
+        <v>52</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>9180000</v>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="20">
+        <f>C4*D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>SDR handoff SLA now under 24h</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>3 — Business case</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>31</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>6420000</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E5" s="20">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Security review is the long pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>4 — Negotiation</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E6" s="20">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>Three deals pending legal redlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>5 — Verbal</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>2260000</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>Two slipped from Q3 into Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Total pipeline</t>
+        </is>
+      </c>
+      <c r="B8" s="32">
+        <f>SUM(B3:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="33">
+        <f>SUM(C3:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="33">
+        <f>SUM(E3:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="34" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Weighted pipeline covers 3.1× the Q4 new-ARR plan; board target is 3.0×.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F7"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:F10"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;9 &amp;K1F4E79Northstar Analytics — FY2026 Q3 Board Pack&amp;R&amp;9 &amp;KC00000CONFIDENTIAL</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K595959Prepared by Priya Shah, VP Finance · 17 August 2026&amp;R&amp;8 &amp;K595959&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D6DCE4"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Headcount — Q3 plan vs actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>Q2 actual</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>Q3 plan</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>Q3 actual</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Var</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Commentary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3" s="21" t="n">
+        <v>86</v>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3" s="35">
+        <f>D3-C3</f>
+        <v/>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>Three offers out; two backfills paused</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Product &amp; design</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="E4" s="35">
+        <f>D4-C4</f>
+        <v/>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>Design systems hire starts 1 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="E5" s="35">
+        <f>D5-C5</f>
+        <v/>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Two AE ramps pushed to Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Customer success</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" s="35">
+        <f>D6-C6</f>
+        <v/>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>Fully staffed against the renewal book</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" s="35">
+        <f>D7-C7</f>
+        <v/>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>Holding open the demand-gen lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="35">
+        <f>D8-C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>Includes the new revenue accountant</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>SUM(B3:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="36">
+        <f>SUM(C3:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="36">
+        <f>SUM(D3:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="37">
+        <f>SUM(E3:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="34" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Net 6 under plan; the shortfall funds the Q4 security hires.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F8"/>
+  <mergeCells count="2">
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;9 &amp;K1F4E79Northstar Analytics — FY2026 Q3 Board Pack&amp;R&amp;9 &amp;KC00000CONFIDENTIAL</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K595959Prepared by Priya Shah, VP Finance · 17 August 2026&amp;R&amp;8 &amp;K595959&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>